--- a/registration_forms/038_marathon_event_volunteer_registration_form--registration_forms.xlsx
+++ b/registration_forms/038_marathon_event_volunteer_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,12 +1010,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'cst'}</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'CST'}</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'pst'}</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'PST'}</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'mst'}</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'MST'}</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1145,29 +1145,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'cst'}</t>
+          <t>akst</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'CST'}</t>
+          <t>AKST</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time_zone_choices</t>
+          <t>volunteer_role_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'akst'}</t>
+          <t>water_station</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'AKST'}</t>
+          <t>Water Station</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'water_station'}</t>
+          <t>aid_station</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Water Station'}</t>
+          <t>Aid Station</t>
         </is>
       </c>
     </row>
@@ -1196,29 +1196,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'aid_station'}</t>
+          <t>finish_line</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Aid Station'}</t>
+          <t>Finish Line</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>volunteer_role_choices</t>
+          <t>confirm_availability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'finish_line'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Finish Line'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1230,29 +1230,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>confirm_availability_choices</t>
+          <t>volunteer_shift_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'am'}</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'AM'}</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -1281,29 +1281,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'pm'}</t>
+          <t>all_day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'PM'}</t>
+          <t>All Day</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>volunteer_shift_choices</t>
+          <t>assigned_volunteer_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'all_day'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'All Day'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1315,29 +1315,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>assigned_volunteer_choices</t>
+          <t>confirm_assigned_volunteer_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1349,29 +1349,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>confirm_assigned_volunteer_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1383,29 +1383,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>reset</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'label':_'reset'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'label': 'Reset'}</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
